--- a/forms/trg/Formulir_TRG_emccrg.xlsx
+++ b/forms/trg/Formulir_TRG_emccrg.xlsx
@@ -955,7 +955,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
